--- a/20260929_株式会社チェングロウス御中_LINEOA施策提案【SIM】ver2.0.xlsx
+++ b/20260929_株式会社チェングロウス御中_LINEOA施策提案【SIM】ver2.0.xlsx
@@ -2237,7 +2237,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">サンクス誘導：初期</t>
+      <t xml:space="preserve">サンクス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">誘導ツール：初期</t>
     </r>
     <r>
       <rPr>
@@ -2256,26 +2275,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">万円</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="メイリオ"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通期</t>
+      <t xml:space="preserve">万・月</t>
     </r>
     <r>
       <rPr>
@@ -2294,36 +2294,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">万円　※</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="メイリオ"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">20%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">のコストカット</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="メイリオ"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">OK</t>
+      <t xml:space="preserve">万（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">FMT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の目安）</t>
     </r>
   </si>
   <si>
@@ -6839,31 +6829,31 @@
       </c>
       <c r="D45" s="109" t="n">
         <f aca="false">+SUM(D65:D72)</f>
-        <v>345000</v>
+        <v>445000</v>
       </c>
       <c r="E45" s="110" t="n">
         <f aca="false">SUM(E65:E69)+SUM(E71:E72)</f>
-        <v>315217</v>
+        <v>365217</v>
       </c>
       <c r="F45" s="110" t="n">
         <f aca="false">SUM(F65:F69)+SUM(F71:F72)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="G45" s="110" t="n">
         <f aca="false">SUM(G65:G69)+SUM(G71:G72)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="H45" s="110" t="n">
         <f aca="false">SUM(H65:H69)+SUM(H71:H72)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="I45" s="110" t="n">
         <f aca="false">SUM(I65:I69)+SUM(I71:I72)</f>
-        <v>315196</v>
+        <v>365196</v>
       </c>
       <c r="J45" s="110" t="n">
         <f aca="false">SUM(J65:J69)+SUM(J71:J72)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="K45" s="50"/>
       <c r="L45" s="51"/>
@@ -6879,27 +6869,27 @@
       </c>
       <c r="E46" s="111" t="n">
         <f aca="false">+SUM(E65:E67)/(E28-D28)</f>
-        <v>510.664852444668</v>
+        <v>1361.77293985245</v>
       </c>
       <c r="F46" s="111" t="n">
         <f aca="false">+SUM(F65:F67)/(F28-E28)</f>
-        <v>406.77677083352</v>
+        <v>1084.73805555605</v>
       </c>
       <c r="G46" s="111" t="n">
         <f aca="false">+SUM(G65:G67)/(G28-F28)</f>
-        <v>357.702060438986</v>
+        <v>953.872161170628</v>
       </c>
       <c r="H46" s="111" t="n">
         <f aca="false">+SUM(H65:H67)/(H28-G28)</f>
-        <v>326.933607957564</v>
+        <v>871.822954553504</v>
       </c>
       <c r="I46" s="111" t="n">
         <f aca="false">+SUM(I65:I67)/(I28-H28)</f>
-        <v>327.111150422602</v>
+        <v>872.296401126939</v>
       </c>
       <c r="J46" s="111" t="n">
         <f aca="false">+SUM(J65:J67)/(J28-I28)</f>
-        <v>307.217845178642</v>
+        <v>819.247587143046</v>
       </c>
       <c r="K46" s="50"/>
       <c r="L46" s="51"/>
@@ -6915,27 +6905,27 @@
       </c>
       <c r="E47" s="111" t="n">
         <f aca="false">+E51/E35</f>
-        <v>7104.88980106099</v>
+        <v>8231.8737202438</v>
       </c>
       <c r="F47" s="111" t="n">
         <f aca="false">+F51/F35</f>
-        <v>3072.45063776313</v>
+        <v>3559.82712811429</v>
       </c>
       <c r="G47" s="111" t="n">
         <f aca="false">+G51/G35</f>
-        <v>1842.17161894725</v>
+        <v>2134.39149295658</v>
       </c>
       <c r="H47" s="111" t="n">
         <f aca="false">+H51/H35</f>
-        <v>1576.40607338855</v>
+        <v>1826.46810855137</v>
       </c>
       <c r="I47" s="111" t="n">
         <f aca="false">+I51/I35</f>
-        <v>1209.11067873462</v>
+        <v>1400.9136646124</v>
       </c>
       <c r="J47" s="111" t="n">
         <f aca="false">+J51/J35</f>
-        <v>949.579298441445</v>
+        <v>1100.209098672</v>
       </c>
       <c r="K47" s="50"/>
       <c r="L47" s="51"/>
@@ -6991,23 +6981,23 @@
       </c>
       <c r="F49" s="111" t="n">
         <f aca="false">+IFERROR(F51/SUM(F36:F39),0)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="G49" s="111" t="n">
         <f aca="false">+IFERROR(G51/SUM(G36:G39),0)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="H49" s="111" t="n">
         <f aca="false">+IFERROR(H51/SUM(H36:H39),0)</f>
-        <v>157601.5</v>
+        <v>182601.5</v>
       </c>
       <c r="I49" s="111" t="n">
         <f aca="false">+IFERROR(I51/SUM(I36:I39),0)</f>
-        <v>157598</v>
+        <v>182598</v>
       </c>
       <c r="J49" s="111" t="n">
         <f aca="false">+IFERROR(J51/SUM(J36:J39),0)</f>
-        <v>105067.666666667</v>
+        <v>121734.333333333</v>
       </c>
       <c r="K49" s="50"/>
       <c r="L49" s="51"/>
@@ -7059,31 +7049,31 @@
       </c>
       <c r="D51" s="118" t="n">
         <f aca="false">+D45</f>
-        <v>345000</v>
+        <v>445000</v>
       </c>
       <c r="E51" s="118" t="n">
         <f aca="false">SUM(E45,E50)+E44</f>
-        <v>315217</v>
+        <v>365217</v>
       </c>
       <c r="F51" s="118" t="n">
         <f aca="false">SUM(F45,F50)+F44</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="G51" s="118" t="n">
         <f aca="false">SUM(G45,G50)+G44</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="H51" s="118" t="n">
         <f aca="false">SUM(H45,H50)+H44</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="I51" s="118" t="n">
         <f aca="false">SUM(I45,I50)+I44</f>
-        <v>315196</v>
+        <v>365196</v>
       </c>
       <c r="J51" s="118" t="n">
         <f aca="false">SUM(J45,J50)+J44</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="K51" s="50"/>
       <c r="L51" s="51"/>
@@ -7150,31 +7140,31 @@
       <c r="C55" s="120"/>
       <c r="D55" s="110" t="n">
         <f aca="false">+SUM(D65:D72)</f>
-        <v>345000</v>
+        <v>445000</v>
       </c>
       <c r="E55" s="110" t="n">
         <f aca="false">SUM(E65:E72)+E54</f>
-        <v>315217</v>
+        <v>365217</v>
       </c>
       <c r="F55" s="110" t="n">
         <f aca="false">SUM(F65:F72)+F54</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="G55" s="110" t="n">
         <f aca="false">SUM(G65:G72)+G54</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="H55" s="110" t="n">
         <f aca="false">SUM(H65:H72)+H54</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="I55" s="110" t="n">
         <f aca="false">SUM(I65:I72)+I54</f>
-        <v>315196</v>
+        <v>365196</v>
       </c>
       <c r="J55" s="110" t="n">
         <f aca="false">SUM(J65:J72)+J54</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="K55" s="50"/>
       <c r="L55" s="51"/>
@@ -7190,27 +7180,27 @@
       </c>
       <c r="E56" s="111" t="n">
         <f aca="false">+SUM(E65:E67)/(E28-D28)</f>
-        <v>510.664852444668</v>
+        <v>1361.77293985245</v>
       </c>
       <c r="F56" s="111" t="n">
         <f aca="false">+SUM(F65:F67)/(F28-E28)</f>
-        <v>406.77677083352</v>
+        <v>1084.73805555605</v>
       </c>
       <c r="G56" s="111" t="n">
         <f aca="false">+SUM(G65:G67)/(G28-F28)</f>
-        <v>357.702060438986</v>
+        <v>953.872161170628</v>
       </c>
       <c r="H56" s="111" t="n">
         <f aca="false">+SUM(H65:H67)/(H28-G28)</f>
-        <v>326.933607957564</v>
+        <v>871.822954553504</v>
       </c>
       <c r="I56" s="111" t="n">
         <f aca="false">+SUM(I65:I67)/(I28-H28)</f>
-        <v>327.111150422602</v>
+        <v>872.296401126939</v>
       </c>
       <c r="J56" s="111" t="n">
         <f aca="false">+SUM(J65:J67)/(J28-I28)</f>
-        <v>307.217845178642</v>
+        <v>819.247587143046</v>
       </c>
       <c r="K56" s="50"/>
       <c r="L56" s="51"/>
@@ -7226,27 +7216,27 @@
       </c>
       <c r="E57" s="111" t="n">
         <f aca="false">+E61/E35</f>
-        <v>7104.88980106099</v>
+        <v>8231.8737202438</v>
       </c>
       <c r="F57" s="111" t="n">
         <f aca="false">+F61/F35</f>
-        <v>3072.45063776313</v>
+        <v>3559.82712811429</v>
       </c>
       <c r="G57" s="111" t="n">
         <f aca="false">+G61/G35</f>
-        <v>1842.17161894725</v>
+        <v>2134.39149295658</v>
       </c>
       <c r="H57" s="111" t="n">
         <f aca="false">+H61/H35</f>
-        <v>1576.40607338855</v>
+        <v>1826.46810855137</v>
       </c>
       <c r="I57" s="111" t="n">
         <f aca="false">+I61/I35</f>
-        <v>1209.11067873462</v>
+        <v>1400.9136646124</v>
       </c>
       <c r="J57" s="111" t="n">
         <f aca="false">+J61/J35</f>
-        <v>949.579298441445</v>
+        <v>1100.209098672</v>
       </c>
       <c r="K57" s="50"/>
       <c r="L57" s="51"/>
@@ -7300,23 +7290,23 @@
       </c>
       <c r="F59" s="111" t="n">
         <f aca="false">+IFERROR(F55/F40,0)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="G59" s="111" t="n">
         <f aca="false">+IFERROR(G55/G40,0)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="H59" s="111" t="n">
         <f aca="false">+IFERROR(H55/H40,0)</f>
-        <v>157601.5</v>
+        <v>182601.5</v>
       </c>
       <c r="I59" s="111" t="n">
         <f aca="false">+IFERROR(I55/I40,0)</f>
-        <v>157598</v>
+        <v>182598</v>
       </c>
       <c r="J59" s="111" t="n">
         <f aca="false">+IFERROR(J55/J40,0)</f>
-        <v>105067.666666667</v>
+        <v>121734.333333333</v>
       </c>
       <c r="K59" s="50"/>
       <c r="L59" s="51"/>
@@ -7345,31 +7335,31 @@
       <c r="C61" s="121"/>
       <c r="D61" s="118" t="n">
         <f aca="false">+D55</f>
-        <v>345000</v>
+        <v>445000</v>
       </c>
       <c r="E61" s="118" t="n">
         <f aca="false">+SUM(E65:E72)+E54</f>
-        <v>315217</v>
+        <v>365217</v>
       </c>
       <c r="F61" s="118" t="n">
         <f aca="false">+SUM(F65:F72)+F54</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="G61" s="118" t="n">
         <f aca="false">+SUM(G65:G72)+G54</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="H61" s="118" t="n">
         <f aca="false">+SUM(H65:H72)+H54</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="I61" s="118" t="n">
         <f aca="false">+SUM(I65:I72)+I54</f>
-        <v>315196</v>
+        <v>365196</v>
       </c>
       <c r="J61" s="118" t="n">
         <f aca="false">+SUM(J65:J72)+J54</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="K61" s="50"/>
       <c r="L61" s="51"/>
@@ -7464,25 +7454,25 @@
         <v>0</v>
       </c>
       <c r="D67" s="124" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="F67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="N67" s="52" t="s">
         <v>121</v>
@@ -7681,31 +7671,31 @@
       </c>
       <c r="D73" s="130" t="n">
         <f aca="false">SUM(D65:D72)</f>
-        <v>345000</v>
+        <v>445000</v>
       </c>
       <c r="E73" s="130" t="n">
         <f aca="false">SUM(E65:E72)</f>
-        <v>315217</v>
+        <v>365217</v>
       </c>
       <c r="F73" s="130" t="n">
         <f aca="false">SUM(F65:F72)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="G73" s="130" t="n">
         <f aca="false">SUM(G65:G72)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="H73" s="130" t="n">
         <f aca="false">SUM(H65:H72)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="I73" s="130" t="n">
         <f aca="false">SUM(I65:I72)</f>
-        <v>315196</v>
+        <v>365196</v>
       </c>
       <c r="J73" s="130" t="n">
         <f aca="false">SUM(J65:J72)</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7887,11 +7877,11 @@
       </c>
       <c r="D4" s="111" t="n">
         <f aca="false">+SIM1_通知メッセ有!G51</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="E4" s="111" t="n">
         <f aca="false">+SIM1_通知メッセ有!J51</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="F4" s="111"/>
     </row>
@@ -7906,11 +7896,11 @@
       </c>
       <c r="D5" s="111" t="n">
         <f aca="false">+SIM1_通知メッセ有!G61</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="E5" s="111" t="n">
         <f aca="false">+SIM1_通知メッセ有!J61</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="F5" s="110"/>
     </row>
@@ -8028,11 +8018,11 @@
       </c>
       <c r="D12" s="111" t="n">
         <f aca="false">+D4/D11</f>
-        <v>1842.17161894725</v>
+        <v>2134.39149295658</v>
       </c>
       <c r="E12" s="111" t="n">
         <f aca="false">+E4/E11</f>
-        <v>949.579298441445</v>
+        <v>1100.209098672</v>
       </c>
       <c r="F12" s="111"/>
     </row>
@@ -8047,11 +8037,11 @@
       </c>
       <c r="D13" s="111" t="n">
         <f aca="false">+D5/D11</f>
-        <v>1842.17161894725</v>
+        <v>2134.39149295658</v>
       </c>
       <c r="E13" s="111" t="n">
         <f aca="false">+E5/E11</f>
-        <v>949.579298441445</v>
+        <v>1100.209098672</v>
       </c>
       <c r="F13" s="111"/>
     </row>
@@ -8269,11 +8259,11 @@
       </c>
       <c r="D22" s="123" t="n">
         <f aca="false">+IFERROR(D4/D16,"--")</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="E22" s="123" t="n">
         <f aca="false">+IFERROR(E4/E16,"--")</f>
-        <v>105067.666666667</v>
+        <v>121734.333333333</v>
       </c>
       <c r="F22" s="123"/>
       <c r="R22" s="65"/>
@@ -8293,11 +8283,11 @@
       </c>
       <c r="D23" s="123" t="n">
         <f aca="false">+IFERROR(D5/D16,"--")</f>
-        <v>315203</v>
+        <v>365203</v>
       </c>
       <c r="E23" s="123" t="n">
         <f aca="false">+IFERROR(E5/E16,"--")</f>
-        <v>105067.666666667</v>
+        <v>121734.333333333</v>
       </c>
       <c r="F23" s="123"/>
       <c r="R23" s="65"/>
@@ -10099,31 +10089,31 @@
       </c>
       <c r="D45" s="109" t="n">
         <f aca="false">+SUM(D65:D72)</f>
-        <v>245000</v>
+        <v>345000</v>
       </c>
       <c r="E45" s="110" t="n">
         <f aca="false">SUM(E65:E69)+SUM(E71:E72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="F45" s="110" t="n">
         <f aca="false">SUM(F65:F69)+SUM(F71:F72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="G45" s="110" t="n">
         <f aca="false">SUM(G65:G69)+SUM(G71:G72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="H45" s="110" t="n">
         <f aca="false">SUM(H65:H69)+SUM(H71:H72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="I45" s="110" t="n">
         <f aca="false">SUM(I65:I69)+SUM(I71:I72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="J45" s="110" t="n">
         <f aca="false">SUM(J65:J69)+SUM(J71:J72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="K45" s="50"/>
       <c r="L45" s="51"/>
@@ -10139,27 +10129,27 @@
       </c>
       <c r="E46" s="111" t="n">
         <f aca="false">+SUM(E65:E67)/(E28-D28)</f>
-        <v>574.472454763885</v>
+        <v>1531.92654603703</v>
       </c>
       <c r="F46" s="111" t="n">
         <f aca="false">+SUM(F65:F67)/(F28-E28)</f>
-        <v>443.451113949198</v>
+        <v>1182.53630386453</v>
       </c>
       <c r="G46" s="111" t="n">
         <f aca="false">+SUM(G65:G67)/(G28-F28)</f>
-        <v>385.297435171298</v>
+        <v>1027.45982712346</v>
       </c>
       <c r="H46" s="111" t="n">
         <f aca="false">+SUM(H65:H67)/(H28-G28)</f>
-        <v>350.002187513672</v>
+        <v>933.339166703125</v>
       </c>
       <c r="I46" s="111" t="n">
         <f aca="false">+SUM(I65:I67)/(I28-H28)</f>
-        <v>349.250878693383</v>
+        <v>931.335676515687</v>
       </c>
       <c r="J46" s="111" t="n">
         <f aca="false">+SUM(J65:J67)/(J28-I28)</f>
-        <v>327.82787397477</v>
+        <v>874.207663932719</v>
       </c>
       <c r="K46" s="50"/>
       <c r="L46" s="51"/>
@@ -10175,27 +10165,27 @@
       </c>
       <c r="E47" s="111" t="n">
         <f aca="false">+E51/E35</f>
-        <v>5958.66293232286</v>
+        <v>7226.46355622134</v>
       </c>
       <c r="F47" s="111" t="n">
         <f aca="false">+F51/F35</f>
-        <v>2531.91167638982</v>
+        <v>3070.61628838765</v>
       </c>
       <c r="G47" s="111" t="n">
         <f aca="false">+G51/G35</f>
-        <v>1502.84256140128</v>
+        <v>1822.59629786963</v>
       </c>
       <c r="H47" s="111" t="n">
         <f aca="false">+H51/H35</f>
-        <v>1277.62138931277</v>
+        <v>1549.45572746443</v>
       </c>
       <c r="I47" s="111" t="n">
         <f aca="false">+I51/I35</f>
-        <v>975.89907840242</v>
+        <v>1183.53718019017</v>
       </c>
       <c r="J47" s="111" t="n">
         <f aca="false">+J51/J35</f>
-        <v>764.233538511584</v>
+        <v>926.836419045964</v>
       </c>
       <c r="K47" s="50"/>
       <c r="L47" s="51"/>
@@ -10251,23 +10241,23 @@
       </c>
       <c r="F49" s="111" t="n">
         <f aca="false">+IFERROR(F51/SUM(F36:F39),0)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="G49" s="111" t="n">
         <f aca="false">+IFERROR(G51/SUM(G36:G39),0)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="H49" s="111" t="n">
         <f aca="false">+IFERROR(H51/SUM(H36:H39),0)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="I49" s="111" t="n">
         <f aca="false">+IFERROR(I51/SUM(I36:I39),0)</f>
-        <v>117500</v>
+        <v>142500</v>
       </c>
       <c r="J49" s="111" t="n">
         <f aca="false">+IFERROR(J51/SUM(J36:J39),0)</f>
-        <v>78333.3333333333</v>
+        <v>95000</v>
       </c>
       <c r="K49" s="50"/>
       <c r="L49" s="51"/>
@@ -10319,31 +10309,31 @@
       </c>
       <c r="D51" s="118" t="n">
         <f aca="false">+D45</f>
-        <v>245000</v>
+        <v>345000</v>
       </c>
       <c r="E51" s="118" t="n">
         <f aca="false">SUM(E45,E50)+E44</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="F51" s="118" t="n">
         <f aca="false">SUM(F45,F50)+F44</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="G51" s="118" t="n">
         <f aca="false">SUM(G45,G50)+G44</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="H51" s="118" t="n">
         <f aca="false">SUM(H45,H50)+H44</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="I51" s="118" t="n">
         <f aca="false">SUM(I45,I50)+I44</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="J51" s="118" t="n">
         <f aca="false">SUM(J45,J50)+J44</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="K51" s="50"/>
       <c r="L51" s="51"/>
@@ -10410,31 +10400,31 @@
       <c r="C55" s="120"/>
       <c r="D55" s="110" t="n">
         <f aca="false">+SUM(D65:D72)</f>
-        <v>245000</v>
+        <v>345000</v>
       </c>
       <c r="E55" s="110" t="n">
         <f aca="false">SUM(E65:E72)+E54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="F55" s="110" t="n">
         <f aca="false">SUM(F65:F72)+F54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="G55" s="110" t="n">
         <f aca="false">SUM(G65:G72)+G54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="H55" s="110" t="n">
         <f aca="false">SUM(H65:H72)+H54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="I55" s="110" t="n">
         <f aca="false">SUM(I65:I72)+I54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="J55" s="110" t="n">
         <f aca="false">SUM(J65:J72)+J54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="K55" s="50"/>
       <c r="L55" s="51"/>
@@ -10450,27 +10440,27 @@
       </c>
       <c r="E56" s="111" t="n">
         <f aca="false">+SUM(E65:E67)/(E28-D28)</f>
-        <v>574.472454763885</v>
+        <v>1531.92654603703</v>
       </c>
       <c r="F56" s="111" t="n">
         <f aca="false">+SUM(F65:F67)/(F28-E28)</f>
-        <v>443.451113949198</v>
+        <v>1182.53630386453</v>
       </c>
       <c r="G56" s="111" t="n">
         <f aca="false">+SUM(G65:G67)/(G28-F28)</f>
-        <v>385.297435171298</v>
+        <v>1027.45982712346</v>
       </c>
       <c r="H56" s="111" t="n">
         <f aca="false">+SUM(H65:H67)/(H28-G28)</f>
-        <v>350.002187513672</v>
+        <v>933.339166703125</v>
       </c>
       <c r="I56" s="111" t="n">
         <f aca="false">+SUM(I65:I67)/(I28-H28)</f>
-        <v>349.250878693383</v>
+        <v>931.335676515687</v>
       </c>
       <c r="J56" s="111" t="n">
         <f aca="false">+SUM(J65:J67)/(J28-I28)</f>
-        <v>327.82787397477</v>
+        <v>874.207663932719</v>
       </c>
       <c r="K56" s="50"/>
       <c r="L56" s="51"/>
@@ -10486,27 +10476,27 @@
       </c>
       <c r="E57" s="111" t="n">
         <f aca="false">+E61/E35</f>
-        <v>5958.66293232286</v>
+        <v>7226.46355622134</v>
       </c>
       <c r="F57" s="111" t="n">
         <f aca="false">+F61/F35</f>
-        <v>2531.91167638982</v>
+        <v>3070.61628838765</v>
       </c>
       <c r="G57" s="111" t="n">
         <f aca="false">+G61/G35</f>
-        <v>1502.84256140128</v>
+        <v>1822.59629786963</v>
       </c>
       <c r="H57" s="111" t="n">
         <f aca="false">+H61/H35</f>
-        <v>1277.62138931277</v>
+        <v>1549.45572746443</v>
       </c>
       <c r="I57" s="111" t="n">
         <f aca="false">+I61/I35</f>
-        <v>975.89907840242</v>
+        <v>1183.53718019017</v>
       </c>
       <c r="J57" s="111" t="n">
         <f aca="false">+J61/J35</f>
-        <v>764.233538511584</v>
+        <v>926.836419045964</v>
       </c>
       <c r="K57" s="50"/>
       <c r="L57" s="51"/>
@@ -10560,23 +10550,23 @@
       </c>
       <c r="F59" s="111" t="n">
         <f aca="false">+IFERROR(F55/F40,0)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="G59" s="111" t="n">
         <f aca="false">+IFERROR(G55/G40,0)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="H59" s="111" t="n">
         <f aca="false">+IFERROR(H55/H40,0)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="I59" s="111" t="n">
         <f aca="false">+IFERROR(I55/I40,0)</f>
-        <v>117500</v>
+        <v>142500</v>
       </c>
       <c r="J59" s="111" t="n">
         <f aca="false">+IFERROR(J55/J40,0)</f>
-        <v>78333.3333333333</v>
+        <v>95000</v>
       </c>
       <c r="K59" s="50"/>
       <c r="L59" s="51"/>
@@ -10605,31 +10595,31 @@
       <c r="C61" s="121"/>
       <c r="D61" s="118" t="n">
         <f aca="false">+D55</f>
-        <v>245000</v>
+        <v>345000</v>
       </c>
       <c r="E61" s="118" t="n">
         <f aca="false">+SUM(E65:E72)+E54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="F61" s="118" t="n">
         <f aca="false">+SUM(F65:F72)+F54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="G61" s="118" t="n">
         <f aca="false">+SUM(G65:G72)+G54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="H61" s="118" t="n">
         <f aca="false">+SUM(H65:H72)+H54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="I61" s="118" t="n">
         <f aca="false">+SUM(I65:I72)+I54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="J61" s="118" t="n">
         <f aca="false">+SUM(J65:J72)+J54</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="K61" s="50"/>
       <c r="L61" s="51"/>
@@ -10724,25 +10714,25 @@
         <v>0</v>
       </c>
       <c r="D67" s="124" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="F67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J67" s="111" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="N67" s="52" t="s">
         <v>121</v>
@@ -10941,31 +10931,31 @@
       </c>
       <c r="D73" s="130" t="n">
         <f aca="false">SUM(D65:D72)</f>
-        <v>245000</v>
+        <v>345000</v>
       </c>
       <c r="E73" s="130" t="n">
         <f aca="false">SUM(E65:E72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="F73" s="130" t="n">
         <f aca="false">SUM(F65:F72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="G73" s="130" t="n">
         <f aca="false">SUM(G65:G72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="H73" s="130" t="n">
         <f aca="false">SUM(H65:H72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="I73" s="130" t="n">
         <f aca="false">SUM(I65:I72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="J73" s="130" t="n">
         <f aca="false">SUM(J65:J72)</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11147,11 +11137,11 @@
       </c>
       <c r="D4" s="111" t="n">
         <f aca="false">+SIM2_通知メッセ無!G51</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="E4" s="111" t="n">
         <f aca="false">+SIM2_通知メッセ無!J51</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="F4" s="111"/>
     </row>
@@ -11166,11 +11156,11 @@
       </c>
       <c r="D5" s="111" t="n">
         <f aca="false">+SIM2_通知メッセ無!G61</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="E5" s="111" t="n">
         <f aca="false">+SIM2_通知メッセ無!J61</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="F5" s="110"/>
     </row>
@@ -11288,11 +11278,11 @@
       </c>
       <c r="D12" s="111" t="n">
         <f aca="false">+D4/D11</f>
-        <v>1502.84256140128</v>
+        <v>1822.59629786963</v>
       </c>
       <c r="E12" s="111" t="n">
         <f aca="false">+E4/E11</f>
-        <v>764.233538511584</v>
+        <v>926.836419045964</v>
       </c>
       <c r="F12" s="111"/>
     </row>
@@ -11307,11 +11297,11 @@
       </c>
       <c r="D13" s="111" t="n">
         <f aca="false">+D5/D11</f>
-        <v>1502.84256140128</v>
+        <v>1822.59629786963</v>
       </c>
       <c r="E13" s="111" t="n">
         <f aca="false">+E5/E11</f>
-        <v>764.233538511584</v>
+        <v>926.836419045964</v>
       </c>
       <c r="F13" s="111"/>
     </row>
@@ -11529,11 +11519,11 @@
       </c>
       <c r="D22" s="123" t="n">
         <f aca="false">+IFERROR(D4/D16,"--")</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="E22" s="123" t="n">
         <f aca="false">+IFERROR(E4/E16,"--")</f>
-        <v>78333.3333333333</v>
+        <v>95000</v>
       </c>
       <c r="F22" s="123"/>
       <c r="R22" s="65"/>
@@ -11553,11 +11543,11 @@
       </c>
       <c r="D23" s="123" t="n">
         <f aca="false">+IFERROR(D5/D16,"--")</f>
-        <v>235000</v>
+        <v>285000</v>
       </c>
       <c r="E23" s="123" t="n">
         <f aca="false">+IFERROR(E5/E16,"--")</f>
-        <v>78333.3333333333</v>
+        <v>95000</v>
       </c>
       <c r="F23" s="123"/>
       <c r="R23" s="65"/>

--- a/20260929_株式会社チェングロウス御中_LINEOA施策提案【SIM】ver2.0.xlsx
+++ b/20260929_株式会社チェングロウス御中_LINEOA施策提案【SIM】ver2.0.xlsx
@@ -1739,11 +1739,7 @@
       <c r="H10" s="147" t="n">
         <v>45</v>
       </c>
-      <c r="I10" s="148" t="inlineStr">
-        <is>
-          <t>リード（イメージ）</t>
-        </is>
-      </c>
+      <c r="I10" s="148" t="n"/>
       <c r="J10" s="139" t="n"/>
       <c r="K10" s="140" t="n"/>
       <c r="N10" s="155" t="inlineStr">
@@ -1775,11 +1771,7 @@
       <c r="H11" s="150" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="151" t="inlineStr">
-        <is>
-          <t>マネタイズ（イメージ）</t>
-        </is>
-      </c>
+      <c r="I11" s="151" t="n"/>
       <c r="J11" s="141" t="n"/>
       <c r="K11" s="142" t="n"/>
     </row>
@@ -5398,11 +5390,7 @@
       <c r="H10" s="147" t="n">
         <v>45</v>
       </c>
-      <c r="I10" s="148" t="inlineStr">
-        <is>
-          <t>リード（イメージ）</t>
-        </is>
-      </c>
+      <c r="I10" s="148" t="n"/>
       <c r="J10" s="139" t="n"/>
       <c r="K10" s="140" t="n"/>
       <c r="N10" s="155" t="inlineStr">
@@ -5434,11 +5422,7 @@
       <c r="H11" s="150" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="151" t="inlineStr">
-        <is>
-          <t>マネタイズ（イメージ）</t>
-        </is>
-      </c>
+      <c r="I11" s="151" t="n"/>
       <c r="J11" s="141" t="n"/>
       <c r="K11" s="142" t="n"/>
     </row>

--- a/20260929_株式会社チェングロウス御中_LINEOA施策提案【SIM】ver2.0.xlsx
+++ b/20260929_株式会社チェングロウス御中_LINEOA施策提案【SIM】ver2.0.xlsx
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C9" s="38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>求人応募（リッチメニュー経由）</t>
         </is>
       </c>
       <c r="D9" s="160" t="n">
@@ -3010,31 +3010,36 @@
         <v/>
       </c>
       <c r="E35" s="50">
-        <f>+E31+E33+1.05*(E31+E33)</f>
+        <f>+E31+E33+1.05*(E31+E33)+E29*0.3*2</f>
         <v/>
       </c>
       <c r="F35" s="50">
-        <f>+F31+F33+1.05*(F31+F33)</f>
+        <f>+F31+F33+1.05*(F31+F33)+F29*0.3*2</f>
         <v/>
       </c>
       <c r="G35" s="50">
-        <f>+G31+G33+1.05*(G31+G33)</f>
+        <f>+G31+G33+1.05*(G31+G33)+G29*0.3*2</f>
         <v/>
       </c>
       <c r="H35" s="50">
-        <f>+H31+H33+1.05*(H31+H33)</f>
+        <f>+H31+H33+1.05*(H31+H33)+H29*0.3*2</f>
         <v/>
       </c>
       <c r="I35" s="50">
-        <f>+I31+I33+1.05*(I31+I33)</f>
+        <f>+I31+I33+1.05*(I31+I33)+I29*0.3*2</f>
         <v/>
       </c>
       <c r="J35" s="50">
-        <f>+J31+J33+1.05*(J31+J33)</f>
+        <f>+J31+J33+1.05*(J31+J33)+J29*0.3*2</f>
         <v/>
       </c>
       <c r="K35" s="11" t="n"/>
       <c r="L35" s="7" t="n"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>＋リッチメニューのタップ：有効な友だち×月に使う率30%×2回</t>
+        </is>
+      </c>
       <c r="O35" s="17" t="inlineStr">
         <is>
           <t>動線の強さ</t>
@@ -3111,23 +3116,29 @@
       <c r="D37" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="111" t="n">
-        <v>0</v>
+      <c r="E37" s="111">
+        <f>ROUND(E29*0.3*2*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="F37" s="111">
+        <f>ROUND(F29*0.3*2*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="111">
+        <f>ROUND(G29*0.3*2*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="111">
+        <f>ROUND(H29*0.3*2*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="I37" s="111">
+        <f>ROUND(I29*0.3*2*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="J37" s="111">
+        <f>ROUND(J29*0.3*2*0.015,0)</f>
+        <v/>
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
@@ -3136,7 +3147,7 @@
       <c r="L37" s="7" t="n"/>
       <c r="N37" s="69" t="inlineStr">
         <is>
-          <t>新規向け_</t>
+          <t>リッチメニュー経由の応募：有効な友だち×月に使う率30%×2回検索×応募率1.5%</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5343,7 @@
       </c>
       <c r="C9" s="38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>求人応募（リッチメニュー経由）</t>
         </is>
       </c>
       <c r="D9" s="160" t="n">
@@ -6661,31 +6672,36 @@
         <v/>
       </c>
       <c r="E35" s="50">
-        <f>+E31+E33+1.05*(E31+E33)</f>
+        <f>+E31+E33+1.05*(E31+E33)+E29*0.3*2</f>
         <v/>
       </c>
       <c r="F35" s="50">
-        <f>+F31+F33+1.05*(F31+F33)</f>
+        <f>+F31+F33+1.05*(F31+F33)+F29*0.3*2</f>
         <v/>
       </c>
       <c r="G35" s="50">
-        <f>+G31+G33+1.05*(G31+G33)</f>
+        <f>+G31+G33+1.05*(G31+G33)+G29*0.3*2</f>
         <v/>
       </c>
       <c r="H35" s="50">
-        <f>+H31+H33+1.05*(H31+H33)</f>
+        <f>+H31+H33+1.05*(H31+H33)+H29*0.3*2</f>
         <v/>
       </c>
       <c r="I35" s="50">
-        <f>+I31+I33+1.05*(I31+I33)</f>
+        <f>+I31+I33+1.05*(I31+I33)+I29*0.3*2</f>
         <v/>
       </c>
       <c r="J35" s="50">
-        <f>+J31+J33+1.05*(J31+J33)</f>
+        <f>+J31+J33+1.05*(J31+J33)+J29*0.3*2</f>
         <v/>
       </c>
       <c r="K35" s="11" t="n"/>
       <c r="L35" s="7" t="n"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>＋リッチメニューのタップ：有効な友だち×月に使う率30%×2回</t>
+        </is>
+      </c>
       <c r="O35" s="17" t="inlineStr">
         <is>
           <t>動線の強さ</t>
@@ -6762,23 +6778,29 @@
       <c r="D37" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="111" t="n">
-        <v>0</v>
+      <c r="E37" s="111">
+        <f>ROUND(E29*0.3*2*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="F37" s="111">
+        <f>ROUND(F29*0.3*2*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="111">
+        <f>ROUND(G29*0.3*2*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="111">
+        <f>ROUND(H29*0.3*2*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="I37" s="111">
+        <f>ROUND(I29*0.3*2*0.015,0)</f>
+        <v/>
+      </c>
+      <c r="J37" s="111">
+        <f>ROUND(J29*0.3*2*0.015,0)</f>
+        <v/>
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
@@ -6787,7 +6809,7 @@
       <c r="L37" s="7" t="n"/>
       <c r="N37" s="69" t="inlineStr">
         <is>
-          <t>新規向け_</t>
+          <t>リッチメニュー経由の応募：有効な友だち×月に使う率30%×2回検索×応募率1.5%</t>
         </is>
       </c>
     </row>
